--- a/reports/pdf_rolling5_20260806.xlsx
+++ b/reports/pdf_rolling5_20260806.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,232억   ·   현금 231억(5.1%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 15종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,384억   ·   현금 230억(5.1%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 15종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>5078700000</v>
+        <v>5068800000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-475263720</v>
+        <v>-474337280</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>92</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>923153760</v>
+        <v>921354240</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-40</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-593028000</v>
+        <v>-591872000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>62</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1784316600</v>
+        <v>1780838400</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1842183000</v>
+        <v>-1838592000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>54</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>763467120</v>
+        <v>761978880</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-23</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-731538000</v>
+        <v>-730112000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2466196200</v>
+        <v>2461388800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-19</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1035131400</v>
+        <v>-1033113600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2092732200</v>
+        <v>2088652800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-17</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2372112000</v>
+        <v>-2367488000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3487374000</v>
+        <v>3480576000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-14</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1745226000</v>
+        <v>-1741824000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>26</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>850964400</v>
+        <v>849305600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-240391800</v>
+        <v>-4257792000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.33%</t>
+          <t>5.12%→2.92%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>75→64</t>
+          <t>43→32</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2569822200</v>
+        <v>2564812800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-4266108000</v>
+        <v>-239923200</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>5.12%→2.92%</t>
+          <t>0.32%→0.33%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>43→32</t>
+          <t>75→64</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>464983200</v>
+        <v>464076800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-10</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-4965840000</v>
+        <v>-4956160000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>814849200</v>
+        <v>813260800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-383724000</v>
+        <v>-382976000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>4831434000</v>
+        <v>4822016000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>473499000</v>
+        <v>472576000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1241460000</v>
+        <v>1239040000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>393060600</v>
+        <v>392294400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,729억   ·   현금 28억(0.7%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,753억   ·   현금 28억(0.7%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1350,7 +1350,7 @@
         <v>45</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>6519195000</v>
+        <v>6544125000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>-21</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-2090064900</v>
+        <v>-2098057500</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>3898965000</v>
+        <v>3913875000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,367억   ·   현금 99억(4.0%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,439억   ·   현금 99억(4.0%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1511,7 +1511,7 @@
         <v>142</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4863500000</v>
+        <v>4849300000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>-41</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1623313000</v>
+        <v>-1618573400</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>50</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>3527750000</v>
+        <v>3517450000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>-17</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4401810000</v>
+        <v>-4388958000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1639890000</v>
+        <v>1635102000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>-10</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1657700000</v>
+        <v>-1652860000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>887623000</v>
+        <v>885031400</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>-7</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-685205500</v>
+        <v>-683204900</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,168억   ·   현금 28억(1.3%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 5종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,175억   ·   현금 28억(1.3%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1973,7 +1973,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 261억   ·   현금 14억(5.0%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 10종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 14억(4.9%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 10종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2069,11 +2069,11 @@
         <v>43</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>87558750</v>
+        <v>95460000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.56%</t>
+          <t>2.38%→2.73%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2090,11 +2090,11 @@
         <v>-145</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-40128750</v>
+        <v>-41651250</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.66%</t>
+          <t>2.87%→2.70%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2113,11 +2113,11 @@
         <v>33</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>91080000</v>
+        <v>92812500</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>7.26%→7.57%</t>
+          <t>7.23%→7.54%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2134,11 +2134,11 @@
         <v>-98</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-91581000</v>
+        <v>-95844000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.62%</t>
+          <t>2.03%→1.66%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2157,11 +2157,11 @@
         <v>24</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>31860000</v>
+        <v>31626000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>3.26%→3.36%</t>
+          <t>3.16%→3.26%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2178,11 +2178,11 @@
         <v>-91</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-52552500</v>
+        <v>-55282500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.85%</t>
+          <t>1.09%→0.87%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2194,23 +2194,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>40725000</v>
+        <v>76725000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.11%</t>
+          <t>3.31%→3.58%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>168→183</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2222,11 +2222,11 @@
         <v>-22</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-32488500</v>
+        <v>-31762500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>3.12%→2.97%</t>
+          <t>2.98%→2.84%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2238,23 +2238,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>75262500</v>
+        <v>43368750</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>3.32%→3.60%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>168→183</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2266,11 +2266,11 @@
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-30030000</v>
+        <v>-29767500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>6.85%→6.69%</t>
+          <t>6.64%→6.48%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2289,11 +2289,11 @@
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>20338500</v>
+        <v>26407500</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.16%</t>
+          <t>0.10%→0.20%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2310,11 +2310,11 @@
         <v>-11</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-20460000</v>
+        <v>-22522500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.29%→0.20%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2333,7 +2333,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>55770000</v>
+        <v>57007500</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
         <v>-8</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-32940000</v>
+        <v>-33540000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.76%</t>
+          <t>0.89%→0.75%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2377,11 +2377,11 @@
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>94500000</v>
+        <v>95775000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.04%</t>
+          <t>2.66%→3.01%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2398,11 +2398,11 @@
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-113400000</v>
+        <v>-113850000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>1.79%→1.33%</t>
+          <t>1.75%→1.31%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2421,11 +2421,11 @@
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>27855000</v>
+        <v>29925000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.07%</t>
+          <t>1.02%→1.13%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2449,11 +2449,11 @@
         <v>6</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>43425000</v>
+        <v>43965000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.54%→2.69%</t>
+          <t>2.51%→2.67%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 501억   ·   현금 27억(5.4%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 8종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 27억(5.4%)      오늘 2026-08-06  vs  5일전 2026-07-30      매수 8종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260806.xlsx
+++ b/reports/pdf_rolling5_20260806.xlsx
@@ -2414,23 +2414,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>29925000</v>
+        <v>43965000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.13%</t>
+          <t>2.51%→2.67%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G56" s="17" t="n"/>
@@ -2442,23 +2442,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>43965000</v>
+        <v>29925000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.51%→2.67%</t>
+          <t>1.02%→1.13%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G57" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260806.xlsx
+++ b/reports/pdf_rolling5_20260806.xlsx
@@ -2194,23 +2194,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>76725000</v>
+        <v>43368750</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.58%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>168→183</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2238,23 +2238,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>43368750</v>
+        <v>76725000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.15%</t>
+          <t>3.31%→3.58%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>168→183</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260806.xlsx
+++ b/reports/pdf_rolling5_20260806.xlsx
@@ -2194,23 +2194,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>43368750</v>
+        <v>76725000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.15%</t>
+          <t>3.31%→3.58%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>168→183</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2238,23 +2238,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>76725000</v>
+        <v>43368750</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.58%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>168→183</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2414,23 +2414,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>43965000</v>
+        <v>29925000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.51%→2.67%</t>
+          <t>1.02%→1.13%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G56" s="17" t="n"/>
@@ -2442,23 +2442,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>29925000</v>
+        <v>43965000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.13%</t>
+          <t>2.51%→2.67%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G57" s="17" t="n"/>
